--- a/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlPositionAnalysis001.xlsx
+++ b/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlPositionAnalysis001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16635" windowHeight="3540"/>
+    <workbookView xWindow="930" yWindow="360" windowWidth="16635" windowHeight="3540"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>资产代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,6 +71,10 @@
   </si>
   <si>
     <t>规模占比%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盈亏(元)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -156,17 +160,17 @@
     <xf numFmtId="177" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="23.375" style="1" customWidth="1"/>
@@ -482,85 +486,90 @@
     <col min="5" max="5" width="19.375" style="1" customWidth="1"/>
     <col min="6" max="6" width="21" style="3" customWidth="1"/>
     <col min="7" max="7" width="17.125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15.75" style="4" customWidth="1"/>
-    <col min="9" max="9" width="21" style="4" customWidth="1"/>
-    <col min="10" max="10" width="14.5" style="4" customWidth="1"/>
-    <col min="11" max="11" width="15.5" style="4" customWidth="1"/>
-    <col min="12" max="12" width="15.875" style="4" customWidth="1"/>
-    <col min="13" max="13" width="14.5" style="4" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="8" max="9" width="15.75" style="4" customWidth="1"/>
+    <col min="10" max="10" width="21" style="4" customWidth="1"/>
+    <col min="11" max="11" width="14.5" style="4" customWidth="1"/>
+    <col min="12" max="12" width="15.5" style="4" customWidth="1"/>
+    <col min="13" max="13" width="15.875" style="4" customWidth="1"/>
+    <col min="14" max="14" width="14.5" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
     </row>
-    <row r="2" spans="1:13" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="5" t="s">
+    <row r="2" spans="1:14" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="H1:H2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="I1:I2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
